--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/126.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/126.xlsx
@@ -426,13 +426,13 @@
         <v>-11.60120699978884</v>
       </c>
       <c r="E2">
-        <v>-27.06158763034668</v>
+        <v>-33.20721140547418</v>
       </c>
       <c r="F2">
-        <v>-3.389759911141156</v>
+        <v>-4.492326864676132</v>
       </c>
       <c r="G2">
-        <v>-15.57040225606572</v>
+        <v>-19.05566018089917</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.31363946968395</v>
       </c>
       <c r="E3">
-        <v>-27.39761398713785</v>
+        <v>-33.44071763920569</v>
       </c>
       <c r="F3">
-        <v>-3.321010386913214</v>
+        <v>-4.33918741128799</v>
       </c>
       <c r="G3">
-        <v>-15.72281480687545</v>
+        <v>-18.63764090620094</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.90382126142094</v>
       </c>
       <c r="E4">
-        <v>-27.26604370331899</v>
+        <v>-33.21423054018607</v>
       </c>
       <c r="F4">
-        <v>-3.324332968565843</v>
+        <v>-4.428292407704925</v>
       </c>
       <c r="G4">
-        <v>-15.16885129015259</v>
+        <v>-18.74796152575161</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.40421684645387</v>
       </c>
       <c r="E5">
-        <v>-27.97950478322746</v>
+        <v>-34.17820000948785</v>
       </c>
       <c r="F5">
-        <v>-3.283440611726645</v>
+        <v>-4.416603315284021</v>
       </c>
       <c r="G5">
-        <v>-15.40794219954429</v>
+        <v>-18.6036862958774</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.81663946459344</v>
       </c>
       <c r="E6">
-        <v>-28.05452801211253</v>
+        <v>-34.29044955895298</v>
       </c>
       <c r="F6">
-        <v>-3.322172586379342</v>
+        <v>-4.433851581345112</v>
       </c>
       <c r="G6">
-        <v>-14.79482419985296</v>
+        <v>-18.5876433921941</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.158818722804346</v>
       </c>
       <c r="E7">
-        <v>-28.50735277050953</v>
+        <v>-34.61916016598474</v>
       </c>
       <c r="F7">
-        <v>-3.442516974290651</v>
+        <v>-4.429108349596682</v>
       </c>
       <c r="G7">
-        <v>-14.5661101954541</v>
+        <v>-18.21603134486536</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.455099864746966</v>
       </c>
       <c r="E8">
-        <v>-28.5291800152265</v>
+        <v>-34.52641022559665</v>
       </c>
       <c r="F8">
-        <v>-3.371772741356768</v>
+        <v>-4.311517454932278</v>
       </c>
       <c r="G8">
-        <v>-14.53099192837351</v>
+        <v>-17.83074674445945</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.728708472634287</v>
       </c>
       <c r="E9">
-        <v>-29.51315401845716</v>
+        <v>-35.08404651490117</v>
       </c>
       <c r="F9">
-        <v>-3.254031912192457</v>
+        <v>-4.435779192291426</v>
       </c>
       <c r="G9">
-        <v>-14.35947421925664</v>
+        <v>-17.81655609100536</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.001399442651108</v>
       </c>
       <c r="E10">
-        <v>-29.76687536015892</v>
+        <v>-35.63460253509471</v>
       </c>
       <c r="F10">
-        <v>-3.270111351848199</v>
+        <v>-4.367390836251105</v>
       </c>
       <c r="G10">
-        <v>-14.01556978281884</v>
+        <v>-17.64617886482677</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.309703975551393</v>
       </c>
       <c r="E11">
-        <v>-30.09453762545791</v>
+        <v>-35.89490374952961</v>
       </c>
       <c r="F11">
-        <v>-3.19983017629248</v>
+        <v>-4.394679743601529</v>
       </c>
       <c r="G11">
-        <v>-13.85580616563915</v>
+        <v>-17.41055244134191</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.679476952284997</v>
       </c>
       <c r="E12">
-        <v>-30.08828380285332</v>
+        <v>-36.22283093055805</v>
       </c>
       <c r="F12">
-        <v>-3.201283961084393</v>
+        <v>-4.28909769117551</v>
       </c>
       <c r="G12">
-        <v>-13.70049192166425</v>
+        <v>-17.27512961023971</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.132696725188046</v>
       </c>
       <c r="E13">
-        <v>-31.06676476711268</v>
+        <v>-36.55391672220685</v>
       </c>
       <c r="F13">
-        <v>-3.164902064753439</v>
+        <v>-4.326869588008361</v>
       </c>
       <c r="G13">
-        <v>-13.74399911114135</v>
+        <v>-17.04832579061701</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.699041662605619</v>
       </c>
       <c r="E14">
-        <v>-31.49510633078721</v>
+        <v>-37.44665103113097</v>
       </c>
       <c r="F14">
-        <v>-2.967942804124606</v>
+        <v>-4.295486060585899</v>
       </c>
       <c r="G14">
-        <v>-13.22702100918322</v>
+        <v>-16.729651021734</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.38917656536348</v>
       </c>
       <c r="E15">
-        <v>-32.29929312320234</v>
+        <v>-37.85842743688544</v>
       </c>
       <c r="F15">
-        <v>-2.867894245949287</v>
+        <v>-4.17776925407627</v>
       </c>
       <c r="G15">
-        <v>-13.06146724785535</v>
+        <v>-16.33106464935129</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.202611321506436</v>
       </c>
       <c r="E16">
-        <v>-32.55694970881676</v>
+        <v>-38.2397928754414</v>
       </c>
       <c r="F16">
-        <v>-2.769318525016146</v>
+        <v>-3.984675984116302</v>
       </c>
       <c r="G16">
-        <v>-12.7217357540698</v>
+        <v>-16.33602219129635</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.138300371659975</v>
       </c>
       <c r="E17">
-        <v>-33.63243964326843</v>
+        <v>-38.75746538162824</v>
       </c>
       <c r="F17">
-        <v>-2.657893168930779</v>
+        <v>-3.962802942845381</v>
       </c>
       <c r="G17">
-        <v>-12.37853149801355</v>
+        <v>-16.35226538298478</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.175855687711855</v>
       </c>
       <c r="E18">
-        <v>-34.44972957522477</v>
+        <v>-39.15824891672909</v>
       </c>
       <c r="F18">
-        <v>-2.442330433169875</v>
+        <v>-3.845594753921071</v>
       </c>
       <c r="G18">
-        <v>-12.29146415033072</v>
+        <v>-16.00944846075663</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.288980964167143</v>
       </c>
       <c r="E19">
-        <v>-34.93075087703052</v>
+        <v>-39.83760605888578</v>
       </c>
       <c r="F19">
-        <v>-2.412456191155314</v>
+        <v>-3.679807787026987</v>
       </c>
       <c r="G19">
-        <v>-12.13908967079469</v>
+        <v>-15.93104812129561</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.455776019976064</v>
       </c>
       <c r="E20">
-        <v>-35.0609784683061</v>
+        <v>-40.67833310806881</v>
       </c>
       <c r="F20">
-        <v>-2.210284842828066</v>
+        <v>-3.634951692165393</v>
       </c>
       <c r="G20">
-        <v>-11.94099986790686</v>
+        <v>-15.87647046753519</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.647012159621596</v>
       </c>
       <c r="E21">
-        <v>-36.34629071742917</v>
+        <v>-40.94770032746707</v>
       </c>
       <c r="F21">
-        <v>-2.162720814926721</v>
+        <v>-3.403068461834533</v>
       </c>
       <c r="G21">
-        <v>-12.07751683430978</v>
+        <v>-15.63066411651707</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.838954115570115</v>
       </c>
       <c r="E22">
-        <v>-36.32973008798312</v>
+        <v>-41.3149414555931</v>
       </c>
       <c r="F22">
-        <v>-1.954545459663983</v>
+        <v>-3.302755654457721</v>
       </c>
       <c r="G22">
-        <v>-11.83337734297069</v>
+        <v>-15.60583502497254</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.017303062765478</v>
       </c>
       <c r="E23">
-        <v>-36.62565907167337</v>
+        <v>-41.86446271947589</v>
       </c>
       <c r="F23">
-        <v>-1.774171771174002</v>
+        <v>-3.206829880846136</v>
       </c>
       <c r="G23">
-        <v>-11.77712124262185</v>
+        <v>-15.39417033010093</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.167836694381066</v>
       </c>
       <c r="E24">
-        <v>-37.01151902068194</v>
+        <v>-41.94935575746068</v>
       </c>
       <c r="F24">
-        <v>-1.838461365305272</v>
+        <v>-2.991938951048902</v>
       </c>
       <c r="G24">
-        <v>-11.96214763281172</v>
+        <v>-15.44308198517089</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.286203338484953</v>
       </c>
       <c r="E25">
-        <v>-37.4820319985529</v>
+        <v>-41.92931273150273</v>
       </c>
       <c r="F25">
-        <v>-1.559000024827219</v>
+        <v>-2.946379572262332</v>
       </c>
       <c r="G25">
-        <v>-11.62765673261484</v>
+        <v>-15.65879216669149</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.37607443345754</v>
       </c>
       <c r="E26">
-        <v>-37.66239206133039</v>
+        <v>-42.05584282375105</v>
       </c>
       <c r="F26">
-        <v>-1.59955606450088</v>
+        <v>-3.02740467303236</v>
       </c>
       <c r="G26">
-        <v>-11.89047101134096</v>
+        <v>-15.69162450207721</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.440794800103161</v>
       </c>
       <c r="E27">
-        <v>-37.55127236613018</v>
+        <v>-41.89575447486889</v>
       </c>
       <c r="F27">
-        <v>-1.480204889105527</v>
+        <v>-2.859397681498773</v>
       </c>
       <c r="G27">
-        <v>-11.80255285345454</v>
+        <v>-15.68835202781164</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.491758206690315</v>
       </c>
       <c r="E28">
-        <v>-37.49092592150397</v>
+        <v>-42.02577828481412</v>
       </c>
       <c r="F28">
-        <v>-1.490657228994052</v>
+        <v>-2.878187539296474</v>
       </c>
       <c r="G28">
-        <v>-11.90345166040044</v>
+        <v>-16.01814195334276</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.542679855422287</v>
       </c>
       <c r="E29">
-        <v>-37.41268068336243</v>
+        <v>-42.28606364959</v>
       </c>
       <c r="F29">
-        <v>-1.348624525742646</v>
+        <v>-2.948727165481866</v>
       </c>
       <c r="G29">
-        <v>-11.93707025035174</v>
+        <v>-15.59235282826386</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.601518464953875</v>
       </c>
       <c r="E30">
-        <v>-37.23603170503422</v>
+        <v>-42.45570028591733</v>
       </c>
       <c r="F30">
-        <v>-1.259700941786924</v>
+        <v>-2.638114240454135</v>
       </c>
       <c r="G30">
-        <v>-11.90795069178831</v>
+        <v>-15.85151723053293</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.680424274072461</v>
       </c>
       <c r="E31">
-        <v>-36.90150427313959</v>
+        <v>-41.69770619261743</v>
       </c>
       <c r="F31">
-        <v>-1.3896519064685</v>
+        <v>-2.762094332896332</v>
       </c>
       <c r="G31">
-        <v>-11.8007287428624</v>
+        <v>-16.203747689002</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.789539389147287</v>
       </c>
       <c r="E32">
-        <v>-36.29805794077348</v>
+        <v>-41.47680496628627</v>
       </c>
       <c r="F32">
-        <v>-1.546889293398291</v>
+        <v>-2.989103449429119</v>
       </c>
       <c r="G32">
-        <v>-12.19051899574727</v>
+        <v>-15.93647410543448</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.929446712087095</v>
       </c>
       <c r="E33">
-        <v>-36.64260688564708</v>
+        <v>-41.33452257720227</v>
       </c>
       <c r="F33">
-        <v>-1.494900955198594</v>
+        <v>-2.938393282131942</v>
       </c>
       <c r="G33">
-        <v>-12.091950812861</v>
+        <v>-16.24927100071251</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.103574475187417</v>
       </c>
       <c r="E34">
-        <v>-36.18390190375111</v>
+        <v>-40.93049891894893</v>
       </c>
       <c r="F34">
-        <v>-1.528716569315675</v>
+        <v>-2.700045472589635</v>
       </c>
       <c r="G34">
-        <v>-12.71323096257941</v>
+        <v>-16.10034279908286</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.311873276351101</v>
       </c>
       <c r="E35">
-        <v>-35.21128304909469</v>
+        <v>-40.57089279799983</v>
       </c>
       <c r="F35">
-        <v>-1.534208645196236</v>
+        <v>-2.937540063707059</v>
       </c>
       <c r="G35">
-        <v>-12.75229208939727</v>
+        <v>-16.38177227537631</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.543662603271627</v>
       </c>
       <c r="E36">
-        <v>-35.26710101971323</v>
+        <v>-40.42309699181149</v>
       </c>
       <c r="F36">
-        <v>-1.470121172711249</v>
+        <v>-2.824527555677927</v>
       </c>
       <c r="G36">
-        <v>-12.84200125242044</v>
+        <v>-16.35849251914415</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.792097742543421</v>
       </c>
       <c r="E37">
-        <v>-35.15895200346205</v>
+        <v>-39.95474409604219</v>
       </c>
       <c r="F37">
-        <v>-1.422586137669002</v>
+        <v>-2.738311076394555</v>
       </c>
       <c r="G37">
-        <v>-12.48868327974172</v>
+        <v>-16.17426231515648</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.04868283385586</v>
       </c>
       <c r="E38">
-        <v>-34.30646903575511</v>
+        <v>-39.51956000814207</v>
       </c>
       <c r="F38">
-        <v>-1.413534567058612</v>
+        <v>-2.878193337868294</v>
       </c>
       <c r="G38">
-        <v>-12.41979413761503</v>
+        <v>-16.5653254728012</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.2966447957792</v>
       </c>
       <c r="E39">
-        <v>-34.52753555138755</v>
+        <v>-39.015916714431</v>
       </c>
       <c r="F39">
-        <v>-1.399806034092016</v>
+        <v>-2.87446402782089</v>
       </c>
       <c r="G39">
-        <v>-12.62666019672747</v>
+        <v>-16.53068392427826</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.527650183142101</v>
       </c>
       <c r="E40">
-        <v>-33.81115586998114</v>
+        <v>-38.52534033246906</v>
       </c>
       <c r="F40">
-        <v>-1.411595358968659</v>
+        <v>-2.938779301341647</v>
       </c>
       <c r="G40">
-        <v>-12.85746150008884</v>
+        <v>-16.22940607220412</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.735709766336126</v>
       </c>
       <c r="E41">
-        <v>-33.13747743423006</v>
+        <v>-37.8825528821613</v>
       </c>
       <c r="F41">
-        <v>-1.38923192419528</v>
+        <v>-2.730013320120713</v>
       </c>
       <c r="G41">
-        <v>-12.77225798954461</v>
+        <v>-16.59053858762828</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.910321187605481</v>
       </c>
       <c r="E42">
-        <v>-32.53283332048891</v>
+        <v>-38.09792031325509</v>
       </c>
       <c r="F42">
-        <v>-1.339982996996641</v>
+        <v>-2.742640952808988</v>
       </c>
       <c r="G42">
-        <v>-12.66552269081297</v>
+        <v>-16.57946481279942</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.052109108975541</v>
       </c>
       <c r="E43">
-        <v>-32.07164447059975</v>
+        <v>-37.40298748474901</v>
       </c>
       <c r="F43">
-        <v>-1.242755858195258</v>
+        <v>-2.666501562980672</v>
       </c>
       <c r="G43">
-        <v>-12.87641768384671</v>
+        <v>-16.56856815215691</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.164599810514304</v>
       </c>
       <c r="E44">
-        <v>-31.90755521493181</v>
+        <v>-36.73303598310624</v>
       </c>
       <c r="F44">
-        <v>-1.313331932546373</v>
+        <v>-2.504689102885219</v>
       </c>
       <c r="G44">
-        <v>-12.89094435767303</v>
+        <v>-16.38532780128548</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.246930826486377</v>
       </c>
       <c r="E45">
-        <v>-30.94413595522197</v>
+        <v>-36.26807491436869</v>
       </c>
       <c r="F45">
-        <v>-1.220062733195565</v>
+        <v>-2.64854007258577</v>
       </c>
       <c r="G45">
-        <v>-12.73070733248122</v>
+        <v>-16.48761372681235</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.306729036706473</v>
       </c>
       <c r="E46">
-        <v>-30.52204368567802</v>
+        <v>-35.82989976938651</v>
       </c>
       <c r="F46">
-        <v>-1.162337950731482</v>
+        <v>-2.54457333659521</v>
       </c>
       <c r="G46">
-        <v>-12.87471275289398</v>
+        <v>-16.71129239144597</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.352196759490809</v>
       </c>
       <c r="E47">
-        <v>-30.20437576251396</v>
+        <v>-35.41493758216764</v>
       </c>
       <c r="F47">
-        <v>-1.169642494489368</v>
+        <v>-2.552313601606968</v>
       </c>
       <c r="G47">
-        <v>-12.48767025280671</v>
+        <v>-16.49476781572271</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.386088905740527</v>
       </c>
       <c r="E48">
-        <v>-29.82998870240382</v>
+        <v>-35.00132261596605</v>
       </c>
       <c r="F48">
-        <v>-1.172295755280534</v>
+        <v>-2.56222087574445</v>
       </c>
       <c r="G48">
-        <v>-12.68288319162091</v>
+        <v>-16.58005740045095</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.415526205496336</v>
       </c>
       <c r="E49">
-        <v>-29.46097694094079</v>
+        <v>-35.00358232449588</v>
       </c>
       <c r="F49">
-        <v>-1.081517456709945</v>
+        <v>-2.366462747849677</v>
       </c>
       <c r="G49">
-        <v>-12.55051764932423</v>
+        <v>-16.74655797780306</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.447152272860899</v>
       </c>
       <c r="E50">
-        <v>-28.82198208761445</v>
+        <v>-34.42856348771291</v>
       </c>
       <c r="F50">
-        <v>-1.171214735819881</v>
+        <v>-2.453548184538586</v>
       </c>
       <c r="G50">
-        <v>-12.73491503586164</v>
+        <v>-16.67114375041846</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.482723322313744</v>
       </c>
       <c r="E51">
-        <v>-28.36421223560108</v>
+        <v>-33.73769043615471</v>
       </c>
       <c r="F51">
-        <v>-0.9343033153540281</v>
+        <v>-2.464292938120298</v>
       </c>
       <c r="G51">
-        <v>-12.83717778756972</v>
+        <v>-16.54069832453456</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.525778604904144</v>
       </c>
       <c r="E52">
-        <v>-27.76029041346415</v>
+        <v>-33.37395434691061</v>
       </c>
       <c r="F52">
-        <v>-1.182458166578079</v>
+        <v>-2.436478017469097</v>
       </c>
       <c r="G52">
-        <v>-12.66838962324998</v>
+        <v>-16.86222678367242</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.579845787117238</v>
       </c>
       <c r="E53">
-        <v>-27.22022007483538</v>
+        <v>-33.27749785054723</v>
       </c>
       <c r="F53">
-        <v>-1.057879164503658</v>
+        <v>-2.37865465928408</v>
       </c>
       <c r="G53">
-        <v>-13.10190887216308</v>
+        <v>-17.04650333529765</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.645156711426978</v>
       </c>
       <c r="E54">
-        <v>-27.00097853422803</v>
+        <v>-32.43163098336549</v>
       </c>
       <c r="F54">
-        <v>-1.033423273670809</v>
+        <v>-2.392568746548903</v>
       </c>
       <c r="G54">
-        <v>-12.68319769344714</v>
+        <v>-16.94623022145866</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.722015981100528</v>
       </c>
       <c r="E55">
-        <v>-26.77311025063606</v>
+        <v>-32.51515189372596</v>
       </c>
       <c r="F55">
-        <v>-1.117471087093652</v>
+        <v>-2.435971884985986</v>
       </c>
       <c r="G55">
-        <v>-13.03932962983424</v>
+        <v>-17.0428915301143</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.811659811567679</v>
       </c>
       <c r="E56">
-        <v>-26.18902767312674</v>
+        <v>-31.97651255288362</v>
       </c>
       <c r="F56">
-        <v>-0.9523816055527246</v>
+        <v>-2.301342301213399</v>
       </c>
       <c r="G56">
-        <v>-12.92480792799423</v>
+        <v>-16.9518862885125</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.914481324741724</v>
       </c>
       <c r="E57">
-        <v>-25.52941920611749</v>
+        <v>-31.87455396060092</v>
       </c>
       <c r="F57">
-        <v>-0.9166640598788155</v>
+        <v>-2.375003215772539</v>
       </c>
       <c r="G57">
-        <v>-13.08330691677792</v>
+        <v>-16.87587781820361</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.029336664774036</v>
       </c>
       <c r="E58">
-        <v>-25.6497498174493</v>
+        <v>-31.20781541126659</v>
       </c>
       <c r="F58">
-        <v>-1.078377944253335</v>
+        <v>-2.522079848139592</v>
       </c>
       <c r="G58">
-        <v>-12.89707217746622</v>
+        <v>-16.99632374128614</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.156292783230919</v>
       </c>
       <c r="E59">
-        <v>-25.17203203743214</v>
+        <v>-31.43132730286318</v>
       </c>
       <c r="F59">
-        <v>-1.119453370288551</v>
+        <v>-2.386363446334532</v>
       </c>
       <c r="G59">
-        <v>-13.15311970111007</v>
+        <v>-16.6615961370832</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.296443434917954</v>
       </c>
       <c r="E60">
-        <v>-25.07789411976069</v>
+        <v>-30.91078147991847</v>
       </c>
       <c r="F60">
-        <v>-1.200775026588782</v>
+        <v>-2.472279228250688</v>
       </c>
       <c r="G60">
-        <v>-13.00536674314686</v>
+        <v>-17.21345745738863</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.44692929638868</v>
       </c>
       <c r="E61">
-        <v>-24.84867182244043</v>
+        <v>-31.1178436896822</v>
       </c>
       <c r="F61">
-        <v>-1.138652441583235</v>
+        <v>-2.460399611327141</v>
       </c>
       <c r="G61">
-        <v>-12.9667194345214</v>
+        <v>-17.00001831010797</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.604689494467031</v>
       </c>
       <c r="E62">
-        <v>-24.48718638477815</v>
+        <v>-30.83857043339216</v>
       </c>
       <c r="F62">
-        <v>-1.243729189893547</v>
+        <v>-2.415485530747351</v>
       </c>
       <c r="G62">
-        <v>-13.11690895400152</v>
+        <v>-17.18472026683499</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.768234346427631</v>
       </c>
       <c r="E63">
-        <v>-24.60955933788742</v>
+        <v>-30.73798849720779</v>
       </c>
       <c r="F63">
-        <v>-1.269455796322291</v>
+        <v>-2.627661072198208</v>
       </c>
       <c r="G63">
-        <v>-13.22114148030547</v>
+        <v>-16.9112029943804</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.928786766845343</v>
       </c>
       <c r="E64">
-        <v>-24.63745926624868</v>
+        <v>-30.55484795138959</v>
       </c>
       <c r="F64">
-        <v>-1.265188047463068</v>
+        <v>-2.486616611258342</v>
       </c>
       <c r="G64">
-        <v>-13.1981464309897</v>
+        <v>-17.19971372758235</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.07753832172214</v>
       </c>
       <c r="E65">
-        <v>-24.13778291576833</v>
+        <v>-30.37432939202183</v>
       </c>
       <c r="F65">
-        <v>-1.472690768394733</v>
+        <v>-2.702445252955545</v>
       </c>
       <c r="G65">
-        <v>-12.98660257103027</v>
+        <v>-17.30292826113297</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.20936008570411</v>
       </c>
       <c r="E66">
-        <v>-23.95665754088353</v>
+        <v>-30.47939451747379</v>
       </c>
       <c r="F66">
-        <v>-1.26261430994257</v>
+        <v>-2.722707947995424</v>
       </c>
       <c r="G66">
-        <v>-13.09912801391009</v>
+        <v>-17.06602065652442</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.31141133453693</v>
       </c>
       <c r="E67">
-        <v>-24.09048300475821</v>
+        <v>-29.94730561428353</v>
       </c>
       <c r="F67">
-        <v>-1.600980028066293</v>
+        <v>-2.830468606690806</v>
       </c>
       <c r="G67">
-        <v>-13.12803900810455</v>
+        <v>-17.04307361011896</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.3730043582861</v>
       </c>
       <c r="E68">
-        <v>-24.20307898248493</v>
+        <v>-30.34150927665124</v>
       </c>
       <c r="F68">
-        <v>-1.445936986386518</v>
+        <v>-2.96502943596896</v>
       </c>
       <c r="G68">
-        <v>-13.09923064082181</v>
+        <v>-16.69281292624576</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.39006107988831</v>
       </c>
       <c r="E69">
-        <v>-23.55912545012019</v>
+        <v>-30.15069523162703</v>
       </c>
       <c r="F69">
-        <v>-1.752210094590982</v>
+        <v>-2.893635762991282</v>
       </c>
       <c r="G69">
-        <v>-12.85654116842892</v>
+        <v>-16.91751123890548</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.35329543257501</v>
       </c>
       <c r="E70">
-        <v>-23.81308227247035</v>
+        <v>-30.27863594352874</v>
       </c>
       <c r="F70">
-        <v>-1.686286959941391</v>
+        <v>-3.07694684229159</v>
       </c>
       <c r="G70">
-        <v>-12.98219292437196</v>
+        <v>-16.94862043533801</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.25855665048283</v>
       </c>
       <c r="E71">
-        <v>-23.45700383277322</v>
+        <v>-30.09047105579902</v>
       </c>
       <c r="F71">
-        <v>-1.918852765012158</v>
+        <v>-3.083890217861855</v>
       </c>
       <c r="G71">
-        <v>-13.13232616457791</v>
+        <v>-16.91002775071396</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.11176557746006</v>
       </c>
       <c r="E72">
-        <v>-24.09920484569698</v>
+        <v>-30.40425807673852</v>
       </c>
       <c r="F72">
-        <v>-2.110020080760617</v>
+        <v>-3.152048287764199</v>
       </c>
       <c r="G72">
-        <v>-12.67244173099005</v>
+        <v>-16.46611173353478</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.913395405666511</v>
       </c>
       <c r="E73">
-        <v>-23.79185278632239</v>
+        <v>-29.77168686379207</v>
       </c>
       <c r="F73">
-        <v>-1.974544733869772</v>
+        <v>-3.364294240444294</v>
       </c>
       <c r="G73">
-        <v>-12.86223861730201</v>
+        <v>-16.83504554952224</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.66619176737515</v>
       </c>
       <c r="E74">
-        <v>-23.6569586025819</v>
+        <v>-30.27545016206435</v>
       </c>
       <c r="F74">
-        <v>-2.148545791930016</v>
+        <v>-3.309642701044596</v>
       </c>
       <c r="G74">
-        <v>-12.56777552322045</v>
+        <v>-16.41650817444711</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.381057762252871</v>
       </c>
       <c r="E75">
-        <v>-23.92119958940348</v>
+        <v>-30.59652349768218</v>
       </c>
       <c r="F75">
-        <v>-2.259373066750562</v>
+        <v>-3.283137429257221</v>
       </c>
       <c r="G75">
-        <v>-12.65356831087066</v>
+        <v>-16.62499640087379</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.061425563823004</v>
       </c>
       <c r="E76">
-        <v>-24.04169322579957</v>
+        <v>-30.24083903522372</v>
       </c>
       <c r="F76">
-        <v>-2.492319920826617</v>
+        <v>-3.490406550581296</v>
       </c>
       <c r="G76">
-        <v>-12.29408279185228</v>
+        <v>-16.55769963115149</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.710675695417967</v>
       </c>
       <c r="E77">
-        <v>-24.28354996560123</v>
+        <v>-30.50003756623775</v>
       </c>
       <c r="F77">
-        <v>-2.616316580616869</v>
+        <v>-3.586671126460627</v>
       </c>
       <c r="G77">
-        <v>-12.6401341170723</v>
+        <v>-16.37665748251813</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.340172476313938</v>
       </c>
       <c r="E78">
-        <v>-24.82885522018287</v>
+        <v>-30.87133620707466</v>
       </c>
       <c r="F78">
-        <v>-2.581737211754406</v>
+        <v>-3.628996558906668</v>
       </c>
       <c r="G78">
-        <v>-11.95305356421534</v>
+        <v>-16.32805867400163</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.953571975845819</v>
       </c>
       <c r="E79">
-        <v>-24.34035514355344</v>
+        <v>-30.96114490359478</v>
       </c>
       <c r="F79">
-        <v>-2.457524348072023</v>
+        <v>-3.818350578410398</v>
       </c>
       <c r="G79">
-        <v>-12.44298781966316</v>
+        <v>-16.1533661517126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.553516543053858</v>
       </c>
       <c r="E80">
-        <v>-25.3990127401186</v>
+        <v>-31.20027323780682</v>
       </c>
       <c r="F80">
-        <v>-2.682726795299305</v>
+        <v>-3.753957438353778</v>
       </c>
       <c r="G80">
-        <v>-11.70298819636095</v>
+        <v>-16.19764966411866</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.150877778108299</v>
       </c>
       <c r="E81">
-        <v>-25.40067921855343</v>
+        <v>-31.58964954688234</v>
       </c>
       <c r="F81">
-        <v>-2.741900392350885</v>
+        <v>-3.815506793116588</v>
       </c>
       <c r="G81">
-        <v>-11.65852756976854</v>
+        <v>-15.8130106200929</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.750257238853903</v>
       </c>
       <c r="E82">
-        <v>-25.84940117949947</v>
+        <v>-31.79431845813301</v>
       </c>
       <c r="F82">
-        <v>-2.563746728500407</v>
+        <v>-3.774542368313346</v>
       </c>
       <c r="G82">
-        <v>-11.6202179367881</v>
+        <v>-16.36274657016211</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.355736618167977</v>
       </c>
       <c r="E83">
-        <v>-26.10675435735538</v>
+        <v>-32.06753261620079</v>
       </c>
       <c r="F83">
-        <v>-2.636956182825021</v>
+        <v>-3.980211083815213</v>
       </c>
       <c r="G83">
-        <v>-11.42305177610572</v>
+        <v>-16.06515501054595</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.979551709527753</v>
       </c>
       <c r="E84">
-        <v>-27.11701615220057</v>
+        <v>-32.79679580615902</v>
       </c>
       <c r="F84">
-        <v>-3.020195391525796</v>
+        <v>-3.908269859984284</v>
       </c>
       <c r="G84">
-        <v>-11.51247954275805</v>
+        <v>-16.07201446090332</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.628251308125857</v>
       </c>
       <c r="E85">
-        <v>-27.84690653580886</v>
+        <v>-33.61452047162008</v>
       </c>
       <c r="F85">
-        <v>-2.811353200503804</v>
+        <v>-3.912128395346524</v>
       </c>
       <c r="G85">
-        <v>-11.4405844252817</v>
+        <v>-15.74907570936572</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.308941025199164</v>
       </c>
       <c r="E86">
-        <v>-28.17340045481388</v>
+        <v>-33.72742891405333</v>
       </c>
       <c r="F86">
-        <v>-2.955768288405662</v>
+        <v>-4.140880396894802</v>
       </c>
       <c r="G86">
-        <v>-11.05889176678589</v>
+        <v>-15.83222337113006</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.034812924135054</v>
       </c>
       <c r="E87">
-        <v>-29.77215103237785</v>
+        <v>-34.87952704329276</v>
       </c>
       <c r="F87">
-        <v>-2.88771127932646</v>
+        <v>-4.18439453656386</v>
       </c>
       <c r="G87">
-        <v>-11.75616217881273</v>
+        <v>-15.84572543111197</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.81300608479018</v>
       </c>
       <c r="E88">
-        <v>-30.13097825579764</v>
+        <v>-35.23969243078181</v>
       </c>
       <c r="F88">
-        <v>-3.013256986159947</v>
+        <v>-4.091156815174359</v>
       </c>
       <c r="G88">
-        <v>-11.20097044969479</v>
+        <v>-15.50012599535807</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.651652876654193</v>
       </c>
       <c r="E89">
-        <v>-31.5047270738165</v>
+        <v>-35.97650458691083</v>
       </c>
       <c r="F89">
-        <v>-3.023231358057056</v>
+        <v>-4.323328317361393</v>
       </c>
       <c r="G89">
-        <v>-11.20674404111528</v>
+        <v>-15.63387037987185</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.561123659684609</v>
       </c>
       <c r="E90">
-        <v>-32.24201924819033</v>
+        <v>-37.09749436395457</v>
       </c>
       <c r="F90">
-        <v>-3.058834589029379</v>
+        <v>-4.42696536312564</v>
       </c>
       <c r="G90">
-        <v>-11.34697875015881</v>
+        <v>-15.91665221401809</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.543161576806185</v>
       </c>
       <c r="E91">
-        <v>-33.35131197687226</v>
+        <v>-38.01445148034571</v>
       </c>
       <c r="F91">
-        <v>-3.170656733100687</v>
+        <v>-4.334845937729918</v>
       </c>
       <c r="G91">
-        <v>-11.36288592147501</v>
+        <v>-15.67971481449968</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.600546836407291</v>
       </c>
       <c r="E92">
-        <v>-34.57158628229717</v>
+        <v>-39.11722320645659</v>
       </c>
       <c r="F92">
-        <v>-3.488289243499741</v>
+        <v>-4.44564836152838</v>
       </c>
       <c r="G92">
-        <v>-11.3387421128571</v>
+        <v>-16.15795953364834</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.734524979386132</v>
       </c>
       <c r="E93">
-        <v>-35.50860453854229</v>
+        <v>-39.87733888982908</v>
       </c>
       <c r="F93">
-        <v>-3.585529636179569</v>
+        <v>-4.663151962114043</v>
       </c>
       <c r="G93">
-        <v>-11.60431738656298</v>
+        <v>-16.32462729355018</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.936001668728001</v>
       </c>
       <c r="E94">
-        <v>-37.21330555822673</v>
+        <v>-40.93074119230834</v>
       </c>
       <c r="F94">
-        <v>-3.44684270886807</v>
+        <v>-4.776662318952257</v>
       </c>
       <c r="G94">
-        <v>-12.03517826740804</v>
+        <v>-16.24653980064262</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.197331058421596</v>
       </c>
       <c r="E95">
-        <v>-38.78312145111869</v>
+        <v>-42.31296052095855</v>
       </c>
       <c r="F95">
-        <v>-3.605503230995871</v>
+        <v>-4.782195813202957</v>
       </c>
       <c r="G95">
-        <v>-11.98866841312682</v>
+        <v>-16.12999204493257</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.50920608543619</v>
       </c>
       <c r="E96">
-        <v>-40.13836692434221</v>
+        <v>-43.77148010816401</v>
       </c>
       <c r="F96">
-        <v>-3.782120273314156</v>
+        <v>-5.040139482025889</v>
       </c>
       <c r="G96">
-        <v>-12.10629540668267</v>
+        <v>-16.31719677408728</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.850552573263389</v>
       </c>
       <c r="E97">
-        <v>-41.59160178238071</v>
+        <v>-45.13068799614424</v>
       </c>
       <c r="F97">
-        <v>-3.81384757320878</v>
+        <v>-5.286235840253983</v>
       </c>
       <c r="G97">
-        <v>-12.61746350121937</v>
+        <v>-17.02080853609459</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.209273882512756</v>
       </c>
       <c r="E98">
-        <v>-43.12179126346856</v>
+        <v>-46.41200160271853</v>
       </c>
       <c r="F98">
-        <v>-3.997488342735402</v>
+        <v>-5.218821644279354</v>
       </c>
       <c r="G98">
-        <v>-12.63869071921718</v>
+        <v>-16.88957685564511</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.561526359849201</v>
       </c>
       <c r="E99">
-        <v>-44.8864243724075</v>
+        <v>-47.89858640758652</v>
       </c>
       <c r="F99">
-        <v>-4.114012300185</v>
+        <v>-5.350122847827492</v>
       </c>
       <c r="G99">
-        <v>-12.78712564956148</v>
+        <v>-17.31869638953652</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.894954238165084</v>
       </c>
       <c r="E100">
-        <v>-46.6301880088821</v>
+        <v>-49.27623650596299</v>
       </c>
       <c r="F100">
-        <v>-4.265155388132396</v>
+        <v>-5.664864355990776</v>
       </c>
       <c r="G100">
-        <v>-13.15897936671458</v>
+        <v>-17.7159817175223</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.176224289896541</v>
       </c>
       <c r="E101">
-        <v>-48.50825939171319</v>
+        <v>-50.79589162439049</v>
       </c>
       <c r="F101">
-        <v>-4.334276020956792</v>
+        <v>-5.724629407367955</v>
       </c>
       <c r="G101">
-        <v>-13.56595797203934</v>
+        <v>-17.57768036707371</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.416100561442522</v>
       </c>
       <c r="E102">
-        <v>-50.60720030155739</v>
+        <v>-52.75435134568725</v>
       </c>
       <c r="F102">
-        <v>-4.489374563252555</v>
+        <v>-5.750795048520183</v>
       </c>
       <c r="G102">
-        <v>-13.68610098020503</v>
+        <v>-17.62285938204814</v>
       </c>
     </row>
   </sheetData>
